--- a/data/nzd0582/nzd0582.xlsx
+++ b/data/nzd0582/nzd0582.xlsx
@@ -26909,9 +26909,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0473</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -26959,9 +26965,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0364</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -27009,9 +27021,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0427</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -27059,9 +27077,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0591</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -27109,9 +27133,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0456</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -27159,9 +27189,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0323</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -27209,9 +27245,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.028</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -27259,9 +27301,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0222</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -27309,9 +27357,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0331</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -27359,9 +27413,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.056</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -27409,9 +27469,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0377</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -27459,9 +27525,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0385</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -27509,9 +27581,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.063</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -27559,9 +27637,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -27609,9 +27693,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0409</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -27659,9 +27749,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0316</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -27709,9 +27805,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0408</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -27759,9 +27861,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0291</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -27809,9 +27917,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0425</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -27859,9 +27973,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.07530000000000001</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -27909,9 +28029,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.079</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -27959,9 +28085,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0709</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -28009,9 +28141,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0853</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -28059,9 +28197,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1066</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -28109,9 +28253,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0835</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -28159,9 +28309,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.08409999999999999</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -28209,9 +28365,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.08359999999999999</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -28259,9 +28421,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1845</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
